--- a/LFSR.xlsx
+++ b/LFSR.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coesia-my.sharepoint.com/personal/mark_williamsen_flexlink_com/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{4334DA85-8158-46F0-9EA8-9FF6BEEC64E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D437FC-9B45-443B-9481-A887A4E7EF31}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="28125"/>
+  <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{15B1B0F4-4CBC-4FA0-B047-941BF17B7E83}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="32640" windowHeight="17240"/>
   </bookViews>
   <sheets>
     <sheet name="7bits" sheetId="4" r:id="rId1"/>
@@ -18,8 +12,11 @@
     <sheet name="5bits" sheetId="2" r:id="rId3"/>
     <sheet name="4bits" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="140001" concurrentCalc="0"/>
   <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -77,7 +74,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -141,7 +138,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -155,6 +152,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -180,7 +178,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -215,391 +213,391 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="128"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>33</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>35</c:v>
+                  <c:v>35.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>37</c:v>
+                  <c:v>37.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>39</c:v>
+                  <c:v>39.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>41</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>43</c:v>
+                  <c:v>43.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>45</c:v>
+                  <c:v>45.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>47</c:v>
+                  <c:v>47.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>49</c:v>
+                  <c:v>49.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>51</c:v>
+                  <c:v>51.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>53</c:v>
+                  <c:v>53.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>55</c:v>
+                  <c:v>55.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>57</c:v>
+                  <c:v>57.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>59</c:v>
+                  <c:v>59.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>61</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>63</c:v>
+                  <c:v>63.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>64</c:v>
+                  <c:v>64.0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>65</c:v>
+                  <c:v>65.0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>66</c:v>
+                  <c:v>66.0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>67</c:v>
+                  <c:v>67.0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>68</c:v>
+                  <c:v>68.0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>69</c:v>
+                  <c:v>69.0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>70</c:v>
+                  <c:v>70.0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>71</c:v>
+                  <c:v>71.0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>72</c:v>
+                  <c:v>72.0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>73</c:v>
+                  <c:v>73.0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>74</c:v>
+                  <c:v>74.0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>75</c:v>
+                  <c:v>75.0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>76</c:v>
+                  <c:v>76.0</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>77</c:v>
+                  <c:v>77.0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>78</c:v>
+                  <c:v>78.0</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>79</c:v>
+                  <c:v>79.0</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>80</c:v>
+                  <c:v>80.0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>81</c:v>
+                  <c:v>81.0</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>82</c:v>
+                  <c:v>82.0</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>83</c:v>
+                  <c:v>83.0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>84</c:v>
+                  <c:v>84.0</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>85</c:v>
+                  <c:v>85.0</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>86</c:v>
+                  <c:v>86.0</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>87</c:v>
+                  <c:v>87.0</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>88</c:v>
+                  <c:v>88.0</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>89</c:v>
+                  <c:v>89.0</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>90</c:v>
+                  <c:v>90.0</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>91</c:v>
+                  <c:v>91.0</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>92</c:v>
+                  <c:v>92.0</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>93</c:v>
+                  <c:v>93.0</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>94</c:v>
+                  <c:v>94.0</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>95</c:v>
+                  <c:v>95.0</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>96</c:v>
+                  <c:v>96.0</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>97</c:v>
+                  <c:v>97.0</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>98</c:v>
+                  <c:v>98.0</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>99</c:v>
+                  <c:v>99.0</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>100</c:v>
+                  <c:v>100.0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>101</c:v>
+                  <c:v>101.0</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>102</c:v>
+                  <c:v>102.0</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>103</c:v>
+                  <c:v>103.0</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>104</c:v>
+                  <c:v>104.0</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>105</c:v>
+                  <c:v>105.0</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>106</c:v>
+                  <c:v>106.0</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>107</c:v>
+                  <c:v>107.0</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>108</c:v>
+                  <c:v>108.0</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>109</c:v>
+                  <c:v>109.0</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>110</c:v>
+                  <c:v>110.0</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>111</c:v>
+                  <c:v>111.0</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>112</c:v>
+                  <c:v>112.0</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>113</c:v>
+                  <c:v>113.0</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>114</c:v>
+                  <c:v>114.0</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>115</c:v>
+                  <c:v>115.0</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>116</c:v>
+                  <c:v>116.0</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>117</c:v>
+                  <c:v>117.0</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>118</c:v>
+                  <c:v>118.0</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>119</c:v>
+                  <c:v>119.0</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>120</c:v>
+                  <c:v>120.0</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>121</c:v>
+                  <c:v>121.0</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>122</c:v>
+                  <c:v>122.0</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>123</c:v>
+                  <c:v>123.0</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>124</c:v>
+                  <c:v>124.0</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>125</c:v>
+                  <c:v>125.0</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>126</c:v>
+                  <c:v>126.0</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>127</c:v>
+                  <c:v>127.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-FCA0-42F8-AFBD-465269D26C68}"/>
             </c:ext>
@@ -630,391 +628,391 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="128"/>
                 <c:pt idx="1">
-                  <c:v>-63</c:v>
+                  <c:v>-63.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-63</c:v>
+                  <c:v>-63.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-61</c:v>
+                  <c:v>-61.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-61</c:v>
+                  <c:v>-61.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-59</c:v>
+                  <c:v>-59.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-59</c:v>
+                  <c:v>-59.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-57</c:v>
+                  <c:v>-57.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-57</c:v>
+                  <c:v>-57.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-55</c:v>
+                  <c:v>-55.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-55</c:v>
+                  <c:v>-55.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-53</c:v>
+                  <c:v>-53.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-53</c:v>
+                  <c:v>-53.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-51</c:v>
+                  <c:v>-51.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-51</c:v>
+                  <c:v>-51.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-49</c:v>
+                  <c:v>-49.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-49</c:v>
+                  <c:v>-49.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-47</c:v>
+                  <c:v>-47.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-47</c:v>
+                  <c:v>-47.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-45</c:v>
+                  <c:v>-45.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-45</c:v>
+                  <c:v>-45.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-43</c:v>
+                  <c:v>-43.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-43</c:v>
+                  <c:v>-43.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-41</c:v>
+                  <c:v>-41.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-41</c:v>
+                  <c:v>-41.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-39</c:v>
+                  <c:v>-39.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-39</c:v>
+                  <c:v>-39.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-37</c:v>
+                  <c:v>-37.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-37</c:v>
+                  <c:v>-37.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-35</c:v>
+                  <c:v>-35.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-35</c:v>
+                  <c:v>-35.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-33</c:v>
+                  <c:v>-33.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-33</c:v>
+                  <c:v>-33.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-31</c:v>
+                  <c:v>-31.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-31</c:v>
+                  <c:v>-31.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-29</c:v>
+                  <c:v>-29.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-29</c:v>
+                  <c:v>-29.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-27</c:v>
+                  <c:v>-27.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-27</c:v>
+                  <c:v>-27.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-25</c:v>
+                  <c:v>-25.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-25</c:v>
+                  <c:v>-25.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-23</c:v>
+                  <c:v>-23.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-23</c:v>
+                  <c:v>-23.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-21</c:v>
+                  <c:v>-21.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-21</c:v>
+                  <c:v>-21.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-19</c:v>
+                  <c:v>-19.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-19</c:v>
+                  <c:v>-19.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-17</c:v>
+                  <c:v>-17.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-17</c:v>
+                  <c:v>-17.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-15</c:v>
+                  <c:v>-15.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-15</c:v>
+                  <c:v>-15.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-13</c:v>
+                  <c:v>-13.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-13</c:v>
+                  <c:v>-13.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-11</c:v>
+                  <c:v>-11.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>-11</c:v>
+                  <c:v>-11.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-9</c:v>
+                  <c:v>-9.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-9</c:v>
+                  <c:v>-9.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>64</c:v>
+                  <c:v>64.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-FCA0-42F8-AFBD-465269D26C68}"/>
             </c:ext>
@@ -1028,12 +1026,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="670868544"/>
-        <c:axId val="670869024"/>
+        <c:axId val="-2137380696"/>
+        <c:axId val="-2137260872"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="670868544"/>
+        <c:axId val="-2137380696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1072,10 +1071,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670869024"/>
+        <c:crossAx val="-2137260872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1083,7 +1082,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="670869024"/>
+        <c:axId val="-2137260872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1131,10 +1130,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670868544"/>
+        <c:crossAx val="-2137380696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1148,6 +1147,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1173,14 +1173,14 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -1210,7 +1210,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1222,7 +1222,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1236,6 +1236,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1261,7 +1262,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1303,394 +1304,394 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="128"/>
                 <c:pt idx="0">
-                  <c:v>85</c:v>
+                  <c:v>85.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106</c:v>
+                  <c:v>106.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>117</c:v>
+                  <c:v>117.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>122</c:v>
+                  <c:v>122.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>125</c:v>
+                  <c:v>125.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>126</c:v>
+                  <c:v>126.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>127</c:v>
+                  <c:v>127.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63</c:v>
+                  <c:v>63.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>64</c:v>
+                  <c:v>64.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>65</c:v>
+                  <c:v>65.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>96</c:v>
+                  <c:v>96.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>67</c:v>
+                  <c:v>67.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>33</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>80</c:v>
+                  <c:v>80.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>69</c:v>
+                  <c:v>69.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>98</c:v>
+                  <c:v>98.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>113</c:v>
+                  <c:v>113.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>120</c:v>
+                  <c:v>120.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>79</c:v>
+                  <c:v>79.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>39</c:v>
+                  <c:v>39.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>68</c:v>
+                  <c:v>68.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>81</c:v>
+                  <c:v>81.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>104</c:v>
+                  <c:v>104.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>77</c:v>
+                  <c:v>77.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>102</c:v>
+                  <c:v>102.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>115</c:v>
+                  <c:v>115.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>57</c:v>
+                  <c:v>57.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>92</c:v>
+                  <c:v>92.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>87</c:v>
+                  <c:v>87.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>43</c:v>
+                  <c:v>43.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>74</c:v>
+                  <c:v>74.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>101</c:v>
+                  <c:v>101.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>114</c:v>
+                  <c:v>114.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>121</c:v>
+                  <c:v>121.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>124</c:v>
+                  <c:v>124.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>95</c:v>
+                  <c:v>95.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>47</c:v>
+                  <c:v>47.0</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>66</c:v>
+                  <c:v>66.0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>97</c:v>
+                  <c:v>97.0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>112</c:v>
+                  <c:v>112.0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>71</c:v>
+                  <c:v>71.0</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>35</c:v>
+                  <c:v>35.0</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>72</c:v>
+                  <c:v>72.0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>73</c:v>
+                  <c:v>73.0</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>100</c:v>
+                  <c:v>100.0</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>89</c:v>
+                  <c:v>89.0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>108</c:v>
+                  <c:v>108.0</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>91</c:v>
+                  <c:v>91.0</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>45</c:v>
+                  <c:v>45.0</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>86</c:v>
+                  <c:v>86.0</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>107</c:v>
+                  <c:v>107.0</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>53</c:v>
+                  <c:v>53.0</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>90</c:v>
+                  <c:v>90.0</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>109</c:v>
+                  <c:v>109.0</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>118</c:v>
+                  <c:v>118.0</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>123</c:v>
+                  <c:v>123.0</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>61</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>94</c:v>
+                  <c:v>94.0</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>111</c:v>
+                  <c:v>111.0</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>55</c:v>
+                  <c:v>55.0</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>70</c:v>
+                  <c:v>70.0</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>99</c:v>
+                  <c:v>99.0</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>49</c:v>
+                  <c:v>49.0</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>88</c:v>
+                  <c:v>88.0</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>75</c:v>
+                  <c:v>75.0</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>37</c:v>
+                  <c:v>37.0</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>82</c:v>
+                  <c:v>82.0</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>105</c:v>
+                  <c:v>105.0</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>116</c:v>
+                  <c:v>116.0</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>93</c:v>
+                  <c:v>93.0</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>110</c:v>
+                  <c:v>110.0</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>119</c:v>
+                  <c:v>119.0</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>59</c:v>
+                  <c:v>59.0</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>78</c:v>
+                  <c:v>78.0</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>103</c:v>
+                  <c:v>103.0</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>51</c:v>
+                  <c:v>51.0</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>76</c:v>
+                  <c:v>76.0</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>83</c:v>
+                  <c:v>83.0</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>41</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>84</c:v>
+                  <c:v>84.0</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>85</c:v>
+                  <c:v>85.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8297-4E47-A94D-08CE0FD9E00B}"/>
             </c:ext>
@@ -1706,11 +1707,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1023900336"/>
-        <c:axId val="1023897936"/>
+        <c:axId val="-2137307224"/>
+        <c:axId val="-2137425544"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1023900336"/>
+        <c:axId val="-2137307224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1749,10 +1750,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1023897936"/>
+        <c:crossAx val="-2137425544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1760,7 +1761,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1023897936"/>
+        <c:axId val="-2137425544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1808,10 +1809,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1023900336"/>
+        <c:crossAx val="-2137307224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1826,7 +1827,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -1856,7 +1857,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1868,7 +1869,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1882,6 +1883,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1907,7 +1909,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1942,199 +1944,199 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="64"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>33</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>35</c:v>
+                  <c:v>35.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>37</c:v>
+                  <c:v>37.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>39</c:v>
+                  <c:v>39.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>41</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>43</c:v>
+                  <c:v>43.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>45</c:v>
+                  <c:v>45.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>47</c:v>
+                  <c:v>47.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>49</c:v>
+                  <c:v>49.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>51</c:v>
+                  <c:v>51.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>53</c:v>
+                  <c:v>53.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>55</c:v>
+                  <c:v>55.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>57</c:v>
+                  <c:v>57.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>59</c:v>
+                  <c:v>59.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>61</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>63</c:v>
+                  <c:v>63.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-A7EF-4E9B-8E35-009674D109BF}"/>
             </c:ext>
@@ -2165,199 +2167,199 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="64"/>
                 <c:pt idx="1">
-                  <c:v>-31</c:v>
+                  <c:v>-31.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-31</c:v>
+                  <c:v>-31.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-29</c:v>
+                  <c:v>-29.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-29</c:v>
+                  <c:v>-29.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-27</c:v>
+                  <c:v>-27.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-27</c:v>
+                  <c:v>-27.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-25</c:v>
+                  <c:v>-25.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-25</c:v>
+                  <c:v>-25.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-23</c:v>
+                  <c:v>-23.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-23</c:v>
+                  <c:v>-23.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-21</c:v>
+                  <c:v>-21.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-21</c:v>
+                  <c:v>-21.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-19</c:v>
+                  <c:v>-19.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-19</c:v>
+                  <c:v>-19.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-17</c:v>
+                  <c:v>-17.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-17</c:v>
+                  <c:v>-17.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-15</c:v>
+                  <c:v>-15.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-15</c:v>
+                  <c:v>-15.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13</c:v>
+                  <c:v>-13.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-13</c:v>
+                  <c:v>-13.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-11</c:v>
+                  <c:v>-11.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-11</c:v>
+                  <c:v>-11.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-9</c:v>
+                  <c:v>-9.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-9</c:v>
+                  <c:v>-9.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-A7EF-4E9B-8E35-009674D109BF}"/>
             </c:ext>
@@ -2371,12 +2373,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="2131395280"/>
-        <c:axId val="2131395760"/>
+        <c:axId val="-2137457608"/>
+        <c:axId val="-2137454040"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2131395280"/>
+        <c:axId val="-2137457608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2415,10 +2418,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2131395760"/>
+        <c:crossAx val="-2137454040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2426,7 +2429,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2131395760"/>
+        <c:axId val="-2137454040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2474,10 +2477,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2131395280"/>
+        <c:crossAx val="-2137457608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2491,6 +2494,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2516,14 +2520,14 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -2553,7 +2557,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2565,7 +2569,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2579,6 +2583,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2604,7 +2609,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2646,202 +2651,202 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="64"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>53</c:v>
+                  <c:v>53.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58</c:v>
+                  <c:v>58.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61</c:v>
+                  <c:v>61.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>62</c:v>
+                  <c:v>62.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63</c:v>
+                  <c:v>63.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>32</c:v>
+                  <c:v>32.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>33</c:v>
+                  <c:v>33.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48</c:v>
+                  <c:v>48.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>35</c:v>
+                  <c:v>35.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>40</c:v>
+                  <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>37</c:v>
+                  <c:v>37.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>50</c:v>
+                  <c:v>50.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>57</c:v>
+                  <c:v>57.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>60</c:v>
+                  <c:v>60.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>47</c:v>
+                  <c:v>47.0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>34</c:v>
+                  <c:v>34.0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>49</c:v>
+                  <c:v>49.0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>56</c:v>
+                  <c:v>56.0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>39</c:v>
+                  <c:v>39.0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>36</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>41</c:v>
+                  <c:v>41.0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>52</c:v>
+                  <c:v>52.0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>45</c:v>
+                  <c:v>45.0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>54</c:v>
+                  <c:v>54.0</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>59</c:v>
+                  <c:v>59.0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>46</c:v>
+                  <c:v>46.0</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>55</c:v>
+                  <c:v>55.0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>38</c:v>
+                  <c:v>38.0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>51</c:v>
+                  <c:v>51.0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>44</c:v>
+                  <c:v>44.0</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>43</c:v>
+                  <c:v>43.0</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-FDE1-4A50-9F6A-87445336E645}"/>
             </c:ext>
@@ -2857,11 +2862,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1044590048"/>
-        <c:axId val="1044588608"/>
+        <c:axId val="-2137406904"/>
+        <c:axId val="-2137401640"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1044590048"/>
+        <c:axId val="-2137406904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2900,10 +2905,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1044588608"/>
+        <c:crossAx val="-2137401640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2911,7 +2916,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1044588608"/>
+        <c:axId val="-2137401640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2959,10 +2964,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1044590048"/>
+        <c:crossAx val="-2137406904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2977,7 +2982,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3007,7 +3012,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3019,7 +3024,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3033,6 +3038,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3058,7 +3064,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3105,103 +3111,103 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-04F8-4742-942C-5BE3905495FF}"/>
             </c:ext>
@@ -3244,103 +3250,103 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="1">
-                  <c:v>-15</c:v>
+                  <c:v>-15.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-14</c:v>
+                  <c:v>-14.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-14</c:v>
+                  <c:v>-14.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13</c:v>
+                  <c:v>-13.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11</c:v>
+                  <c:v>-11.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-10</c:v>
+                  <c:v>-10.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-10</c:v>
+                  <c:v>-10.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9</c:v>
+                  <c:v>-9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-6</c:v>
+                  <c:v>-6.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-6</c:v>
+                  <c:v>-6.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2</c:v>
+                  <c:v>-2.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2</c:v>
+                  <c:v>-2.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-04F8-4742-942C-5BE3905495FF}"/>
             </c:ext>
@@ -3356,11 +3362,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="596377232"/>
-        <c:axId val="596377712"/>
+        <c:axId val="-2137224008"/>
+        <c:axId val="-2137181768"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="596377232"/>
+        <c:axId val="-2137224008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3399,10 +3405,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596377712"/>
+        <c:crossAx val="-2137181768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3410,7 +3416,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="596377712"/>
+        <c:axId val="-2137181768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3458,10 +3464,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596377232"/>
+        <c:crossAx val="-2137224008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3475,6 +3481,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3500,14 +3507,14 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3537,7 +3544,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3549,7 +3556,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3563,6 +3570,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3588,7 +3596,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3630,106 +3638,106 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26</c:v>
+                  <c:v>26.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>25.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>28</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>30</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>31</c:v>
+                  <c:v>31.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>24</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>27</c:v>
+                  <c:v>27.0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>29</c:v>
+                  <c:v>29.0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>23</c:v>
+                  <c:v>23.0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-B594-4FF0-B82C-2D05E6D7FD05}"/>
             </c:ext>
@@ -3745,11 +3753,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="682283056"/>
-        <c:axId val="682283536"/>
+        <c:axId val="2135159176"/>
+        <c:axId val="2135419160"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="682283056"/>
+        <c:axId val="2135159176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3788,10 +3796,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="682283536"/>
+        <c:crossAx val="2135419160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3799,7 +3807,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="682283536"/>
+        <c:axId val="2135419160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3847,10 +3855,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="682283056"/>
+        <c:crossAx val="2135159176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3865,7 +3873,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -3895,7 +3903,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3907,7 +3915,7 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3921,6 +3929,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3946,7 +3955,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3993,55 +4002,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-EF7F-428C-960B-EAA53BEC319B}"/>
             </c:ext>
@@ -4084,55 +4093,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="1">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-7</c:v>
+                  <c:v>-7.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-5</c:v>
+                  <c:v>-5.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3</c:v>
+                  <c:v>-3.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1</c:v>
+                  <c:v>-1.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-EF7F-428C-960B-EAA53BEC319B}"/>
             </c:ext>
@@ -4148,11 +4157,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591401360"/>
-        <c:axId val="591404240"/>
+        <c:axId val="2115550776"/>
+        <c:axId val="2135314712"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="591401360"/>
+        <c:axId val="2115550776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4191,10 +4200,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591404240"/>
+        <c:crossAx val="2135314712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4202,7 +4211,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="591404240"/>
+        <c:axId val="2135314712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4250,10 +4259,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591401360"/>
+        <c:crossAx val="2115550776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4267,6 +4276,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4292,14 +4302,14 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -4329,7 +4339,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4341,7 +4351,7 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -4355,6 +4365,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4380,7 +4391,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sv-SE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4422,58 +4433,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-163E-4BAF-BC5A-58E282C0860B}"/>
             </c:ext>
@@ -4489,11 +4500,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1021954320"/>
-        <c:axId val="1021959120"/>
+        <c:axId val="2135915976"/>
+        <c:axId val="2135519928"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1021954320"/>
+        <c:axId val="2135915976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4532,10 +4543,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1021959120"/>
+        <c:crossAx val="2135519928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4543,7 +4554,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1021959120"/>
+        <c:axId val="2135519928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4591,10 +4602,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1021954320"/>
+        <c:crossAx val="2135915976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4609,7 +4620,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -4639,7 +4650,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9066,7 +9077,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C2A5FCD-DAFC-9251-F8C2-BAF2B245C0CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1C2A5FCD-DAFC-9251-F8C2-BAF2B245C0CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9102,7 +9113,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A28A5836-C9B4-1019-3C2F-7132B0975830}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A28A5836-C9B4-1019-3C2F-7132B0975830}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9143,7 +9154,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E66EF1E7-70C4-6FEE-5E12-0A6A12E6BD3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E66EF1E7-70C4-6FEE-5E12-0A6A12E6BD3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9179,7 +9190,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8524F44D-F048-DC5D-C4F3-1073E298CBAD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8524F44D-F048-DC5D-C4F3-1073E298CBAD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9220,7 +9231,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27992160-7174-2B8F-0D19-750ACA18C597}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27992160-7174-2B8F-0D19-750ACA18C597}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9256,7 +9267,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDAD3965-7B34-7BA6-C7DC-7FC4F764A414}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FDAD3965-7B34-7BA6-C7DC-7FC4F764A414}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9297,7 +9308,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E493F15-F57E-3127-CFD0-5E764C10AC8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1E493F15-F57E-3127-CFD0-5E764C10AC8A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9333,7 +9344,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70C20744-FAE4-DA35-59C3-7A1B8FF0CDB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{70C20744-FAE4-DA35-59C3-7A1B8FF0CDB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9397,7 +9408,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -9449,7 +9460,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -9663,21 +9674,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D07FC9-0EC8-42A0-A927-C5C8314EFEA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:L130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.625" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="2" max="9" width="8.88671875" style="1"/>
+    <col min="2" max="9" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12">
       <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
@@ -9685,7 +9696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
@@ -9720,7 +9731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -9751,9 +9762,9 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12">
       <c r="B4" s="1">
-        <f>_xlfn.BITXOR(H3,G3)</f>
+        <f>MOD(H3+G3,2)</f>
         <v>1</v>
       </c>
       <c r="C4" s="1">
@@ -9795,9 +9806,9 @@
         <v>-63</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12">
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B68" si="2">_xlfn.BITXOR(H4,G4)</f>
+        <f t="shared" ref="B5:B68" si="2">MOD(H4+G4,2)</f>
         <v>1</v>
       </c>
       <c r="C5" s="1">
@@ -9839,7 +9850,7 @@
         <v>-63</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12">
       <c r="B6" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -9883,7 +9894,7 @@
         <v>-61</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12">
       <c r="B7" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -9927,7 +9938,7 @@
         <v>-61</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12">
       <c r="B8" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -9971,7 +9982,7 @@
         <v>-59</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12">
       <c r="B9" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10015,7 +10026,7 @@
         <v>-59</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12">
       <c r="B10" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10059,7 +10070,7 @@
         <v>-57</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12">
       <c r="B11" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10103,7 +10114,7 @@
         <v>-57</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12">
       <c r="B12" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10147,7 +10158,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12">
       <c r="B13" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10191,7 +10202,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12">
       <c r="B14" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10235,7 +10246,7 @@
         <v>-53</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12">
       <c r="B15" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10279,7 +10290,7 @@
         <v>-53</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12">
       <c r="B16" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10323,7 +10334,7 @@
         <v>-51</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12">
       <c r="B17" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10367,7 +10378,7 @@
         <v>-51</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12">
       <c r="B18" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10411,7 +10422,7 @@
         <v>-49</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12">
       <c r="B19" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10455,13 +10466,13 @@
         <v>-49</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12">
       <c r="B20" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:H83" si="4">B19</f>
+        <f t="shared" ref="C20:H62" si="4">B19</f>
         <v>0</v>
       </c>
       <c r="D20" s="1">
@@ -10499,7 +10510,7 @@
         <v>-47</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12">
       <c r="B21" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10543,7 +10554,7 @@
         <v>-47</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12">
       <c r="B22" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10587,7 +10598,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12">
       <c r="B23" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10631,7 +10642,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12">
       <c r="B24" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10675,7 +10686,7 @@
         <v>-43</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12">
       <c r="B25" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10719,7 +10730,7 @@
         <v>-43</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12">
       <c r="B26" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10763,7 +10774,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12">
       <c r="B27" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10807,7 +10818,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12">
       <c r="B28" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10851,7 +10862,7 @@
         <v>-39</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12">
       <c r="B29" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10895,7 +10906,7 @@
         <v>-39</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12">
       <c r="B30" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -10939,7 +10950,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12">
       <c r="B31" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -10983,7 +10994,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12">
       <c r="B32" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11027,7 +11038,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12">
       <c r="B33" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11071,7 +11082,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12">
       <c r="B34" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11115,7 +11126,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12">
       <c r="B35" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11159,7 +11170,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12">
       <c r="B36" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11203,7 +11214,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12">
       <c r="B37" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11247,7 +11258,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12">
       <c r="B38" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11291,7 +11302,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12">
       <c r="B39" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11335,7 +11346,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12">
       <c r="B40" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11379,7 +11390,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12">
       <c r="B41" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11423,7 +11434,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12">
       <c r="B42" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11467,7 +11478,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12">
       <c r="B43" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11511,7 +11522,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12">
       <c r="B44" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11555,7 +11566,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12">
       <c r="B45" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11599,7 +11610,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12">
       <c r="B46" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11643,7 +11654,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12">
       <c r="B47" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11687,7 +11698,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12">
       <c r="B48" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11731,7 +11742,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12">
       <c r="B49" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11775,7 +11786,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12">
       <c r="B50" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11819,7 +11830,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12">
       <c r="B51" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11863,7 +11874,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12">
       <c r="B52" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11907,7 +11918,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12">
       <c r="B53" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -11951,7 +11962,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12">
       <c r="B54" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -11995,7 +12006,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12">
       <c r="B55" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12039,7 +12050,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12">
       <c r="B56" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12083,7 +12094,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12">
       <c r="B57" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12127,7 +12138,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12">
       <c r="B58" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12171,7 +12182,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12">
       <c r="B59" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12215,7 +12226,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12">
       <c r="B60" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12259,7 +12270,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12">
       <c r="B61" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12303,7 +12314,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12">
       <c r="B62" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12321,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1">
-        <f t="shared" ref="C62:H125" si="5">E61</f>
+        <f t="shared" ref="C62:H104" si="5">E61</f>
         <v>0</v>
       </c>
       <c r="G62" s="1">
@@ -12347,7 +12358,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12">
       <c r="B63" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12391,7 +12402,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12">
       <c r="B64" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12435,7 +12446,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12">
       <c r="B65" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -12479,7 +12490,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12">
       <c r="B66" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12523,7 +12534,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12">
       <c r="B67" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12567,7 +12578,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12">
       <c r="B68" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12597,7 +12608,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" ref="I68:I131" si="6">H68+2*G68+4*F68+8*E68+16*D68+32*C68+64*B68</f>
+        <f t="shared" ref="I68:I130" si="6">H68+2*G68+4*F68+8*E68+16*D68+32*C68+64*B68</f>
         <v>11</v>
       </c>
       <c r="J68" s="1">
@@ -12611,9 +12622,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12">
       <c r="B69" s="1">
-        <f t="shared" ref="B69:B132" si="7">_xlfn.BITXOR(H68,G68)</f>
+        <f t="shared" ref="B69:B130" si="7">MOD(H68+G68,2)</f>
         <v>0</v>
       </c>
       <c r="C69" s="1">
@@ -12655,7 +12666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12">
       <c r="B70" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -12699,7 +12710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12">
       <c r="B71" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -12743,7 +12754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12">
       <c r="B72" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -12787,7 +12798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12">
       <c r="B73" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -12831,7 +12842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12">
       <c r="B74" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -12875,7 +12886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12">
       <c r="B75" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -12919,7 +12930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12">
       <c r="B76" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -12963,7 +12974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12">
       <c r="B77" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13007,7 +13018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12">
       <c r="B78" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13051,7 +13062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12">
       <c r="B79" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13095,7 +13106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12">
       <c r="B80" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13139,7 +13150,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12">
       <c r="B81" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13183,7 +13194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12">
       <c r="B82" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13227,7 +13238,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12">
       <c r="B83" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13271,7 +13282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12">
       <c r="B84" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13315,7 +13326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12">
       <c r="B85" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13359,7 +13370,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12">
       <c r="B86" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13403,7 +13414,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12">
       <c r="B87" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13447,7 +13458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12">
       <c r="B88" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13491,7 +13502,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12">
       <c r="B89" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13535,7 +13546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12">
       <c r="B90" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13579,7 +13590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12">
       <c r="B91" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13623,7 +13634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12">
       <c r="B92" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13667,7 +13678,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12">
       <c r="B93" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13711,7 +13722,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12">
       <c r="B94" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13755,7 +13766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12">
       <c r="B95" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13799,7 +13810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12">
       <c r="B96" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13843,7 +13854,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12">
       <c r="B97" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -13887,7 +13898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12">
       <c r="B98" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13931,7 +13942,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12">
       <c r="B99" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -13975,7 +13986,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12">
       <c r="B100" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14019,7 +14030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12">
       <c r="B101" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14063,7 +14074,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12">
       <c r="B102" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14107,7 +14118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12">
       <c r="B103" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14151,7 +14162,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12">
       <c r="B104" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14195,13 +14206,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12">
       <c r="B105" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="C105" s="1">
-        <f t="shared" ref="C105:H150" si="9">B104</f>
+        <f t="shared" ref="C105:H130" si="9">B104</f>
         <v>1</v>
       </c>
       <c r="D105" s="1">
@@ -14239,7 +14250,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12">
       <c r="B106" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14283,7 +14294,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12">
       <c r="B107" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14327,7 +14338,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12">
       <c r="B108" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14371,7 +14382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12">
       <c r="B109" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14415,7 +14426,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12">
       <c r="B110" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14459,7 +14470,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12">
       <c r="B111" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14503,7 +14514,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12">
       <c r="B112" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14547,7 +14558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12">
       <c r="B113" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14591,7 +14602,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12">
       <c r="B114" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14635,7 +14646,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12">
       <c r="B115" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14679,7 +14690,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12">
       <c r="B116" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14723,7 +14734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12">
       <c r="B117" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14767,7 +14778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12">
       <c r="B118" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14811,7 +14822,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12">
       <c r="B119" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14855,7 +14866,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12">
       <c r="B120" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14899,7 +14910,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12">
       <c r="B121" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -14943,7 +14954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12">
       <c r="B122" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -14987,7 +14998,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12">
       <c r="B123" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -15031,7 +15042,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12">
       <c r="B124" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -15075,7 +15086,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12">
       <c r="B125" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -15119,7 +15130,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12">
       <c r="B126" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -15163,7 +15174,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12">
       <c r="B127" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -15207,7 +15218,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12">
       <c r="B128" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -15251,7 +15262,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:12">
       <c r="B129" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -15295,7 +15306,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:12">
       <c r="B130" s="1">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -15338,24 +15349,29 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K3:K129">
+  <sortState ref="K3:K129">
     <sortCondition ref="K3:K129"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{110163AE-A26C-47BE-8890-25DEE1297180}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.625" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="2" max="8" width="8.88671875" style="1"/>
-    <col min="10" max="11" width="8.88671875" style="1"/>
+    <col min="2" max="8" width="8.625" style="1"/>
+    <col min="10" max="11" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11">
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
@@ -15363,7 +15379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
@@ -15395,7 +15411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -15422,9 +15438,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11">
       <c r="B4" s="1">
-        <f>_xlfn.BITXOR(G3,F3)</f>
+        <f>MOD(G3+F3,2)</f>
         <v>1</v>
       </c>
       <c r="C4" s="1">
@@ -15462,9 +15478,9 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11">
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B68" si="1">_xlfn.BITXOR(G4,F4)</f>
+        <f t="shared" ref="B5:B66" si="1">MOD(G4+F4,2)</f>
         <v>1</v>
       </c>
       <c r="C5" s="1">
@@ -15488,11 +15504,11 @@
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" ref="H5:H68" si="2">G5+2*F5+4*E5+8*D5+16*C5+32*B5</f>
+        <f t="shared" ref="H5:H66" si="2">G5+2*F5+4*E5+8*D5+16*C5+32*B5</f>
         <v>53</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" ref="I5:I68" si="3">H4-H5</f>
+        <f t="shared" ref="I5:I66" si="3">H4-H5</f>
         <v>-11</v>
       </c>
       <c r="J5" s="1">
@@ -15502,7 +15518,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11">
       <c r="B6" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15542,7 +15558,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15582,7 +15598,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15622,7 +15638,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15662,7 +15678,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15702,7 +15718,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15742,7 +15758,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15782,7 +15798,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15822,7 +15838,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11">
       <c r="B14" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15862,7 +15878,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11">
       <c r="B15" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15902,7 +15918,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11">
       <c r="B16" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15942,7 +15958,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11">
       <c r="B17" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15982,7 +15998,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11">
       <c r="B18" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16022,7 +16038,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11">
       <c r="B19" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16062,13 +16078,13 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11">
       <c r="B20" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:G83" si="4">B19</f>
+        <f t="shared" ref="C20:G66" si="4">B19</f>
         <v>0</v>
       </c>
       <c r="D20" s="1">
@@ -16102,7 +16118,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11">
       <c r="B21" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16142,7 +16158,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11">
       <c r="B22" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16182,7 +16198,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11">
       <c r="B23" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16222,7 +16238,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11">
       <c r="B24" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16262,7 +16278,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11">
       <c r="B25" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16302,7 +16318,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11">
       <c r="B26" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16342,7 +16358,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11">
       <c r="B27" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16382,7 +16398,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11">
       <c r="B28" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16422,7 +16438,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11">
       <c r="B29" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16462,7 +16478,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11">
       <c r="B30" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16502,7 +16518,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11">
       <c r="B31" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16542,7 +16558,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11">
       <c r="B32" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16582,7 +16598,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11">
       <c r="B33" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16622,7 +16638,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11">
       <c r="B34" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16662,7 +16678,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11">
       <c r="B35" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16702,7 +16718,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11">
       <c r="B36" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16742,7 +16758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11">
       <c r="B37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16782,7 +16798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11">
       <c r="B38" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16822,7 +16838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11">
       <c r="B39" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16862,7 +16878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11">
       <c r="B40" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16902,7 +16918,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11">
       <c r="B41" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -16942,7 +16958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11">
       <c r="B42" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16982,7 +16998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11">
       <c r="B43" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17022,7 +17038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11">
       <c r="B44" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17062,7 +17078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11">
       <c r="B45" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17102,7 +17118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11">
       <c r="B46" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17142,7 +17158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11">
       <c r="B47" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17182,7 +17198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11">
       <c r="B48" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17222,7 +17238,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11">
       <c r="B49" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17262,7 +17278,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11">
       <c r="B50" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17302,7 +17318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11">
       <c r="B51" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17342,7 +17358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11">
       <c r="B52" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17382,7 +17398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11">
       <c r="B53" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17422,7 +17438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11">
       <c r="B54" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17462,7 +17478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:11">
       <c r="B55" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17502,7 +17518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11">
       <c r="B56" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17542,7 +17558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11">
       <c r="B57" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17582,7 +17598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:11">
       <c r="B58" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17622,7 +17638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:11">
       <c r="B59" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17662,7 +17678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:11">
       <c r="B60" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17702,7 +17718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:11">
       <c r="B61" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17742,7 +17758,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:11">
       <c r="B62" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17782,7 +17798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:11">
       <c r="B63" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17822,7 +17838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:11">
       <c r="B64" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17862,7 +17878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11">
       <c r="B65" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -17902,7 +17918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11">
       <c r="B66" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -17939,216 +17955,221 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11">
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11">
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:11">
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:11">
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:11">
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:11">
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:11">
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:11">
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:11">
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:11">
       <c r="I76" s="1"/>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:11">
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:11">
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:11">
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:11">
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="9:9">
       <c r="I81" s="1"/>
     </row>
-    <row r="82" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="9:9">
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="9:9">
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="9:9">
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="9:9">
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="9:9">
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="9:9">
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="9:9">
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="9:9">
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="9:9">
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="9:9">
       <c r="I91" s="1"/>
     </row>
-    <row r="92" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="9:9">
       <c r="I92" s="1"/>
     </row>
-    <row r="93" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="9:9">
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="9:9">
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="9:9">
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="9:9">
       <c r="I96" s="1"/>
     </row>
-    <row r="97" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="9:9">
       <c r="I97" s="1"/>
     </row>
-    <row r="98" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="9:9">
       <c r="I98" s="1"/>
     </row>
-    <row r="99" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="9:9">
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="9:9">
       <c r="I100" s="1"/>
     </row>
-    <row r="101" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="9:9">
       <c r="I101" s="1"/>
     </row>
-    <row r="102" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="9:9">
       <c r="I102" s="1"/>
     </row>
-    <row r="103" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="9:9">
       <c r="I103" s="1"/>
     </row>
-    <row r="104" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="9:9">
       <c r="I104" s="1"/>
     </row>
-    <row r="105" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="9:9">
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="9:9">
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="9:9">
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="9:9">
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="9:9">
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="9:9">
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="9:9">
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="9:9">
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="9:9">
       <c r="I113" s="1"/>
     </row>
-    <row r="114" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="9:9">
       <c r="I114" s="1"/>
     </row>
-    <row r="115" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="9:9">
       <c r="I115" s="1"/>
     </row>
-    <row r="116" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="9:9">
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="9:9">
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="9:9">
       <c r="I118" s="1"/>
     </row>
-    <row r="119" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="9:9">
       <c r="I119" s="1"/>
     </row>
-    <row r="120" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="9:9">
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="9:9">
       <c r="I121" s="1"/>
     </row>
-    <row r="122" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="9:9">
       <c r="I122" s="1"/>
     </row>
-    <row r="123" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="9:9">
       <c r="I123" s="1"/>
     </row>
-    <row r="124" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="9:9">
       <c r="I124" s="1"/>
     </row>
-    <row r="125" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="9:9">
       <c r="I125" s="1"/>
     </row>
-    <row r="126" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="9:9">
       <c r="I126" s="1"/>
     </row>
-    <row r="127" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="9:9">
       <c r="I127" s="1"/>
     </row>
-    <row r="128" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="9:9">
       <c r="I128" s="1"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9">
       <c r="I129" s="1"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9">
       <c r="I130" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K4:K66">
+  <sortState ref="K4:K66">
     <sortCondition ref="K4:K66"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9D4D7B-87BE-44BA-B30D-D76C2B015C2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.625" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="9" max="10" width="8.88671875" style="1"/>
+    <col min="9" max="10" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
@@ -18156,7 +18177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -18186,7 +18207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="1"/>
       <c r="B3" s="1">
         <v>1</v>
@@ -18211,14 +18232,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
-        <f>_xlfn.BITXOR(D3,F3)</f>
+        <f>MOD(D3+F3,2)</f>
         <v>0</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="B4:F19" si="0">B3</f>
+        <f t="shared" ref="C4:F19" si="0">B3</f>
         <v>1</v>
       </c>
       <c r="D4" s="1">
@@ -18234,7 +18255,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" ref="G4:G66" si="1">F4+2*E4+4*D4+8*C4+16*B4</f>
+        <f t="shared" ref="G4" si="1">F4+2*E4+4*D4+8*C4+16*B4</f>
         <v>10</v>
       </c>
       <c r="H4" s="1">
@@ -18248,10 +18269,10 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B68" si="2">_xlfn.BITXOR(D4,F4)</f>
+        <f t="shared" ref="B5:B34" si="2">MOD(D4+F4,2)</f>
         <v>0</v>
       </c>
       <c r="C5" s="1">
@@ -18271,11 +18292,11 @@
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5:G68" si="3">F5+2*E5+4*D5+8*C5+16*B5</f>
+        <f t="shared" ref="G5:G34" si="3">F5+2*E5+4*D5+8*C5+16*B5</f>
         <v>5</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" ref="H5:H68" si="4">G4-G5</f>
+        <f t="shared" ref="H5:H34" si="4">G4-G5</f>
         <v>5</v>
       </c>
       <c r="I5" s="1">
@@ -18285,7 +18306,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <f t="shared" si="2"/>
@@ -18322,7 +18343,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <f t="shared" si="2"/>
@@ -18359,7 +18380,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <f t="shared" si="2"/>
@@ -18396,7 +18417,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <f t="shared" si="2"/>
@@ -18433,7 +18454,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <f t="shared" si="2"/>
@@ -18470,7 +18491,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <f t="shared" si="2"/>
@@ -18507,7 +18528,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <f t="shared" si="2"/>
@@ -18544,7 +18565,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <f t="shared" si="2"/>
@@ -18581,7 +18602,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <f t="shared" si="2"/>
@@ -18618,7 +18639,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <f t="shared" si="2"/>
@@ -18655,7 +18676,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <f t="shared" si="2"/>
@@ -18692,7 +18713,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <f t="shared" si="2"/>
@@ -18729,7 +18750,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <f t="shared" si="2"/>
@@ -18766,7 +18787,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <f t="shared" si="2"/>
@@ -18803,14 +18824,14 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:F83" si="5">B19</f>
+        <f t="shared" ref="C20:F34" si="5">B19</f>
         <v>1</v>
       </c>
       <c r="D20" s="1">
@@ -18840,7 +18861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <f t="shared" si="2"/>
@@ -18877,7 +18898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <f t="shared" si="2"/>
@@ -18914,7 +18935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <f t="shared" si="2"/>
@@ -18951,7 +18972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <f t="shared" si="2"/>
@@ -18988,7 +19009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <f t="shared" si="2"/>
@@ -19025,7 +19046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <f t="shared" si="2"/>
@@ -19062,7 +19083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <f t="shared" si="2"/>
@@ -19099,7 +19120,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <f t="shared" si="2"/>
@@ -19136,7 +19157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <f t="shared" si="2"/>
@@ -19173,7 +19194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <f t="shared" si="2"/>
@@ -19210,7 +19231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <f t="shared" si="2"/>
@@ -19247,7 +19268,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <f t="shared" si="2"/>
@@ -19284,7 +19305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <f t="shared" si="2"/>
@@ -19321,7 +19342,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <f t="shared" si="2"/>
@@ -19355,7 +19376,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -19365,7 +19386,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -19375,7 +19396,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -19385,7 +19406,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -19395,7 +19416,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -19405,7 +19426,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -19415,7 +19436,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -19425,7 +19446,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -19435,7 +19456,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -19445,7 +19466,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -19455,7 +19476,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -19465,7 +19486,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -19475,7 +19496,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -19485,7 +19506,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -19495,7 +19516,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -19505,7 +19526,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -19515,7 +19536,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -19525,7 +19546,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -19535,7 +19556,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -19545,7 +19566,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -19555,7 +19576,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -19565,7 +19586,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -19575,7 +19596,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -19585,7 +19606,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -19595,7 +19616,7 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -19605,7 +19626,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -19615,7 +19636,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -19625,7 +19646,7 @@
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -19635,7 +19656,7 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -19645,7 +19666,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -19655,7 +19676,7 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -19665,7 +19686,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -19675,7 +19696,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -19684,7 +19705,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -19693,7 +19714,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -19702,7 +19723,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -19711,7 +19732,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -19720,7 +19741,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -19729,7 +19750,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -19738,7 +19759,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -19747,7 +19768,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -19756,7 +19777,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -19765,7 +19786,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -19774,7 +19795,7 @@
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -19783,7 +19804,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -19792,7 +19813,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -19801,7 +19822,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:8">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -19810,7 +19831,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:8">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -19819,7 +19840,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:8">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -19828,7 +19849,7 @@
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:8">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -19837,7 +19858,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:8">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -19846,7 +19867,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:8">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -19855,7 +19876,7 @@
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:8">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -19864,7 +19885,7 @@
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:8">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -19873,7 +19894,7 @@
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:8">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -19882,7 +19903,7 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:8">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -19891,7 +19912,7 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:8">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -19900,141 +19921,146 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:8">
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:8">
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:8">
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:8">
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:8">
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="8:8">
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="8:8">
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="8:8">
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="8:8">
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="8:8">
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="8:8">
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="8:8">
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="8:8">
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="8:8">
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="8:8">
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="8:8">
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="8:8">
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="8:8">
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="8:8">
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="8:8">
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="8:8">
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:8">
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:8">
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:8">
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:8">
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:8">
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:8">
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:8">
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:8">
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:8">
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:8">
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:8">
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:8">
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:8">
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:8">
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:8">
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:8">
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:8">
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:8">
       <c r="H130" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J4:J34">
+  <sortState ref="J4:J34">
     <sortCondition ref="J4:J34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004E91CC-F9AF-458D-A6F9-D3BF2010BD51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.625" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="8" max="9" width="8.88671875" style="1"/>
+    <col min="8" max="9" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
@@ -20042,7 +20068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -20069,7 +20095,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="1"/>
       <c r="B3" s="1">
         <v>0</v>
@@ -20091,14 +20117,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
-        <f>_xlfn.BITXOR(E3,D3)</f>
+        <f>MOD(E3+D3,2)</f>
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="B4:F19" si="0">B3</f>
+        <f t="shared" ref="C4:E18" si="0">B3</f>
         <v>0</v>
       </c>
       <c r="D4" s="1">
@@ -20110,7 +20136,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:F20" si="1">E4+2*D4+4*C4+8*B4</f>
+        <f t="shared" ref="F4:F18" si="1">E4+2*D4+4*C4+8*B4</f>
         <v>10</v>
       </c>
       <c r="G4" s="1">
@@ -20124,10 +20150,10 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B68" si="2">_xlfn.BITXOR(E4,D4)</f>
+        <f t="shared" ref="B5:B18" si="2">MOD(E4+D4,2)</f>
         <v>1</v>
       </c>
       <c r="C5" s="1">
@@ -20147,7 +20173,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5:G68" si="3">F4-F5</f>
+        <f t="shared" ref="G5:G18" si="3">F4-F5</f>
         <v>-3</v>
       </c>
       <c r="H5" s="1">
@@ -20157,7 +20183,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <f t="shared" si="2"/>
@@ -20190,7 +20216,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <f t="shared" si="2"/>
@@ -20223,7 +20249,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <f t="shared" si="2"/>
@@ -20256,7 +20282,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <f t="shared" si="2"/>
@@ -20289,7 +20315,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <f t="shared" si="2"/>
@@ -20322,7 +20348,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <f t="shared" si="2"/>
@@ -20355,7 +20381,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <f t="shared" si="2"/>
@@ -20388,7 +20414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <f t="shared" si="2"/>
@@ -20421,7 +20447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <f t="shared" si="2"/>
@@ -20454,7 +20480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <f t="shared" si="2"/>
@@ -20487,7 +20513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <f t="shared" si="2"/>
@@ -20520,7 +20546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <f t="shared" si="2"/>
@@ -20553,7 +20579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <f t="shared" si="2"/>
@@ -20583,7 +20609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20592,7 +20618,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -20601,7 +20627,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -20610,7 +20636,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -20619,7 +20645,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -20628,7 +20654,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -20637,7 +20663,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -20646,7 +20672,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -20655,7 +20681,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -20664,7 +20690,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -20673,7 +20699,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -20682,7 +20708,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -20691,7 +20717,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -20700,7 +20726,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -20709,7 +20735,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -20718,7 +20744,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -20727,7 +20753,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -20736,7 +20762,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -20745,7 +20771,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -20754,7 +20780,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -20763,7 +20789,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -20772,7 +20798,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -20781,7 +20807,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -20790,7 +20816,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -20799,7 +20825,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -20808,7 +20834,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -20817,7 +20843,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -20826,7 +20852,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -20835,7 +20861,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -20844,7 +20870,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -20853,7 +20879,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -20862,7 +20888,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -20871,7 +20897,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -20880,7 +20906,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -20889,7 +20915,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -20898,7 +20924,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -20907,7 +20933,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -20916,7 +20942,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -20925,7 +20951,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -20934,7 +20960,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -20943,7 +20969,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -20952,7 +20978,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -20961,7 +20987,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -20970,7 +20996,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -20979,7 +21005,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -20988,7 +21014,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -20997,7 +21023,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -21006,7 +21032,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -21014,7 +21040,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -21022,7 +21048,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -21030,7 +21056,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -21038,7 +21064,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -21046,7 +21072,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -21054,7 +21080,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -21062,7 +21088,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -21070,7 +21096,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -21078,7 +21104,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -21086,177 +21112,182 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7">
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7">
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="7:7">
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="7:7">
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="7:7">
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="7:7">
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="7:7">
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="7:7">
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="7:7">
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="7:7">
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="7:7">
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="7:7">
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="7:7">
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="7:7">
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="7:7">
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="7:7">
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="7:7">
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="7:7">
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="7:7">
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="7:7">
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="7:7">
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="7:7">
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="7:7">
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="7:7">
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="7:7">
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="7:7">
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="7:7">
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="7:7">
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="7:7">
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="7:7">
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="7:7">
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="7:7">
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="7:7">
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="7:7">
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="7:7">
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="7:7">
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="7:7">
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="7:7">
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="7:7">
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="7:7">
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="7:7">
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="7:7">
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="7:7">
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="7:7">
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="7:7">
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="7:7">
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="7:7">
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="7:7">
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="7:7">
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="7:7">
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="7:7">
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="7:7">
       <c r="G130" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H17">
+  <sortState ref="H3:H17">
     <sortCondition ref="H3:H17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
